--- a/evals/1_inputs/excel/test_dataset_50.xlsx
+++ b/evals/1_inputs/excel/test_dataset_50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Samuel\Projects\Skripsi\TravelPlanner\TravelPlannerLLMRAGMCP\evals\1_inputs\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9560D3F-DA86-433D-9189-F716E1682EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6CF46F-7B16-4713-A2A8-6BFE1601ADF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{303DDD28-EEF9-48CD-845F-90282090C77A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="138">
   <si>
     <t>id</t>
   </si>
@@ -314,12 +314,6 @@
     <t>Apakah ada peringatan gelombang tinggi atau angin kencang di perairan Labuan Bajo hari ini?</t>
   </si>
   <si>
-    <t>Bagaimana kondisi cuaca di Likupang Minahasa Utara sepanjang minggu ini untuk aktivitas snorkeling?</t>
-  </si>
-  <si>
-    <t>Apakah bulan September besok wilayah Lombok Tengah sudah memasuki musim kemarau?</t>
-  </si>
-  <si>
     <t>Cari tahu apakah sore ini akan terjadi badai petir di sekitar Bandara Internasional Komodo.</t>
   </si>
   <si>
@@ -438,6 +432,27 @@
   </si>
   <si>
     <t>Cari hotel keluarga dengan akses langsung ke dermaga kapal di Labuan Bajo tanggal 24/12/2026 28/12/2026</t>
+  </si>
+  <si>
+    <t>Bandung</t>
+  </si>
+  <si>
+    <t>Toba</t>
+  </si>
+  <si>
+    <t>Magelang</t>
+  </si>
+  <si>
+    <t>Mandalika</t>
+  </si>
+  <si>
+    <t>Bagaimana kondisi cuaca di Likupang sepanjang minggu ini untuk aktivitas snorkeling?</t>
+  </si>
+  <si>
+    <t>Apakah bulan September besok wilayah Lombok sudah memasuki musim kemarau?</t>
+  </si>
+  <si>
+    <t>Samosir</t>
   </si>
 </sst>
 </file>
@@ -1067,6 +1082,9 @@
       <c r="C22" t="s">
         <v>11</v>
       </c>
+      <c r="F22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1078,6 +1096,9 @@
       <c r="C23" t="s">
         <v>87</v>
       </c>
+      <c r="F23" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1089,6 +1110,9 @@
       <c r="C24" t="s">
         <v>88</v>
       </c>
+      <c r="F24" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1100,6 +1124,9 @@
       <c r="C25" t="s">
         <v>89</v>
       </c>
+      <c r="F25" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1111,6 +1138,9 @@
       <c r="C26" t="s">
         <v>90</v>
       </c>
+      <c r="F26" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1120,7 +1150,10 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>135</v>
+      </c>
+      <c r="F27" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -1131,7 +1164,10 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>136</v>
+      </c>
+      <c r="F28" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -1142,7 +1178,10 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="F29" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -1153,7 +1192,10 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="F30" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -1164,7 +1206,10 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>93</v>
+      </c>
+      <c r="F31" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -1175,7 +1220,7 @@
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -1198,13 +1243,13 @@
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G33" s="1">
         <v>46307</v>
@@ -1221,13 +1266,13 @@
         <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G34" s="1">
         <v>46285</v>
@@ -1244,13 +1289,13 @@
         <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" t="s">
         <v>102</v>
-      </c>
-      <c r="E35" t="s">
-        <v>104</v>
       </c>
       <c r="G35" s="1">
         <v>46200</v>
@@ -1267,13 +1312,13 @@
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G36" s="1">
         <v>46249</v>
@@ -1290,13 +1335,13 @@
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G37" s="1">
         <v>46296</v>
@@ -1310,13 +1355,13 @@
         <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G38" s="1">
         <v>46283</v>
@@ -1330,13 +1375,13 @@
         <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G39" s="1">
         <v>46207</v>
@@ -1350,13 +1395,13 @@
         <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G40" s="1">
         <v>46381</v>
@@ -1370,13 +1415,13 @@
         <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G41" s="1">
         <v>46208</v>
@@ -1390,7 +1435,7 @@
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
@@ -1410,10 +1455,10 @@
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G43" s="1">
         <v>46285</v>
@@ -1430,10 +1475,10 @@
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F44" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G44" s="1">
         <v>46307</v>
@@ -1450,10 +1495,10 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G45" s="1">
         <v>46270</v>
@@ -1470,10 +1515,10 @@
         <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G46" s="1">
         <v>46296</v>
@@ -1490,10 +1535,10 @@
         <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F47" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G47" s="1">
         <v>46249</v>
@@ -1510,10 +1555,10 @@
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F48" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G48" s="1">
         <v>46306</v>
@@ -1527,10 +1572,10 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G49" s="1">
         <v>46340</v>
@@ -1547,10 +1592,10 @@
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F50" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G50" s="1">
         <v>46225</v>
@@ -1564,10 +1609,10 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G51" s="1">
         <v>46380</v>
